--- a/template.xlsx
+++ b/template.xlsx
@@ -918,7 +918,16 @@
     <col width="2.88671875" customWidth="1" style="23" min="1" max="1"/>
     <col width="40.21875" customWidth="1" style="23" min="2" max="2"/>
     <col width="18.33203125" bestFit="1" customWidth="1" style="23" min="3" max="9"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="17.77734375" bestFit="1" customWidth="1" style="23" min="10" max="13"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
     <col width="23.77734375" bestFit="1" customWidth="1" style="23" min="14" max="14"/>
     <col width="19.44140625" bestFit="1" customWidth="1" style="11" min="15" max="15"/>
     <col width="8.77734375" customWidth="1" style="23" min="16" max="16"/>
@@ -3957,7 +3966,16 @@
     <col width="1.5546875" customWidth="1" style="23" min="1" max="1"/>
     <col width="40.21875" customWidth="1" style="23" min="2" max="2"/>
     <col width="18.33203125" bestFit="1" customWidth="1" style="23" min="3" max="9"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="18.6640625" bestFit="1" customWidth="1" style="23" min="10" max="13"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
     <col width="23.77734375" bestFit="1" customWidth="1" style="23" min="14" max="14"/>
     <col width="19.44140625" bestFit="1" customWidth="1" style="11" min="15" max="15"/>
     <col width="19.44140625" bestFit="1" customWidth="1" style="47" min="16" max="16"/>
@@ -5093,7 +5111,16 @@
     <col width="1.5546875" customWidth="1" style="23" min="1" max="1"/>
     <col width="40.21875" customWidth="1" style="23" min="2" max="2"/>
     <col width="18.33203125" bestFit="1" customWidth="1" style="23" min="3" max="9"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="18.6640625" bestFit="1" customWidth="1" style="23" min="10" max="13"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
     <col width="23.77734375" bestFit="1" customWidth="1" style="23" min="14" max="14"/>
     <col width="19.44140625" bestFit="1" customWidth="1" style="11" min="15" max="15"/>
     <col width="19.44140625" bestFit="1" customWidth="1" style="47" min="16" max="16"/>
@@ -6224,7 +6251,16 @@
     <col width="1.5546875" customWidth="1" min="1" max="1"/>
     <col width="40.21875" customWidth="1" min="2" max="2"/>
     <col width="18.33203125" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="18.6640625" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
     <col width="23.77734375" customWidth="1" min="14" max="14"/>
     <col width="19.44140625" customWidth="1" min="15" max="15"/>
     <col width="19.44140625" customWidth="1" min="16" max="16"/>
@@ -7359,7 +7395,12 @@
     <col width="18.109375" customWidth="1" style="23" min="5" max="5"/>
     <col width="19.109375" customWidth="1" style="23" min="6" max="6"/>
     <col width="18.33203125" bestFit="1" customWidth="1" style="23" min="7" max="9"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="17.77734375" bestFit="1" customWidth="1" style="23" min="10" max="13"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
     <col width="23.77734375" bestFit="1" customWidth="1" style="23" min="14" max="14"/>
     <col width="20.109375" bestFit="1" customWidth="1" style="11" min="15" max="15"/>
     <col width="19.44140625" customWidth="1" style="23" min="16" max="16"/>
